--- a/stories/arbres/ATOM-REL.CON.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amine est au parc avec papa. Papa s'assoit sur le banc. Amine joue près du toboggan. Un camarade arrive vite. Le camarade bouscule Amine. Amine sent un choc. Son cœur bat vite. Amine dit : stop. Il fait un pas de côté. Il doit s'éloigner. S'éloigner, c'est marcher vers papa. Amine marche vers le banc. Papa est son parent au parc. Amine rejoint son parent au parc. Il dit : on m'a bousculé. Papa l'écoute. Papa dit : tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Amine souffle. Plus tard, près du bac à sable, un autre camarade bouscule encore. Amine se souvient. Il dit : stop. Il s'éloigne. Il rejoint son parent au parc. Même leçon, autre coin du parc. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
+          <t>Amine est au parc avec papa. Papa s'assoit sur le banc. Amine joue près du toboggan. Un camarade arrive vite. Le camarade bouscule Amine. Amine sent un choc. Son cœur bat vite. Stop. Il fait un pas de côté. Il doit s'éloigner. S'éloigner, c'est marcher vers papa. Amine marche vers le banc. Papa est son parent au parc. Amine rejoint son parent au parc. On m'a bousculé. Papa l'écoute. Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Amine souffle. Plus tard, près du bac à sable, un autre camarade bouscule encore. Amine se souvient. Stop. Il s'éloigne. Il rejoint son parent au parc. Même leçon, autre coin du parc. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Amine est au parc avec papa. Papa s'assoit sur le banc. Amine joue près du toboggan. Un camarade arrive vite. Le camarade bouscule Amine. Amine sent un choc. Son cœur bat vite.
+enfant-f|Stop. Il fait un pas de côté. Il doit s'éloigner. S'éloigner, c'est marcher vers papa.
+narrateur|Amine marche vers le banc. Papa est son parent au parc. Amine rejoint son parent au parc.
+narrateur|On m'a bousculé. Papa l'écoute.
+papa|Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi.
+narrateur|Amine souffle. Plus tard, près du bac à sable, un autre camarade bouscule encore. Amine se souvient.
+narrateur|Stop.
+narrateur|Il s'éloigne. Il rejoint son parent au parc. Même leçon, autre coin du parc. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Amine. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Amine a dit stop. Il a su s'éloigner. Il a rejoint son parent au parc. Plus tard, pareil.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Amine boit une gorgée d'eau. Papa garde sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Il s'éloigne. Il rejoint son parent au parc. Même leçon, autre coin du parc. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Un camarade bouscule Amine. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,11 @@
           <t>narrateur|Amine a dit stop. Il a su s'éloigner. Il a rejoint son parent au parc. Plus tard, pareil.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1854,7 @@
           <t>narrateur|Amine boit une gorgée d'eau. Papa garde sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2065,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2280,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amine dit stop au parc, deux fois</t>
+          <t>Le toboggan d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le toboggan brille comme du miel. Amir glisse, puis va au bac. Deux fois, il dit stop, s'éloigne, rejoint papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amine est au parc avec papa. Papa s'assoit sur le banc. Amine joue près du toboggan. Un camarade arrive vite. Le camarade bouscule Amine. Amine sent un choc. Son cœur bat vite. Stop. Il fait un pas de côté. Il doit s'éloigner. S'éloigner, c'est marcher vers papa. Amine marche vers le banc. Papa est son parent au parc. Amine rejoint son parent au parc. On m'a bousculé. Papa l'écoute. Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Amine souffle. Plus tard, près du bac à sable, un autre camarade bouscule encore. Amine se souvient. Stop. Il s'éloigne. Il rejoint son parent au parc. Même leçon, autre coin du parc. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
+          <t>Le toboggan de bois brille comme du miel. Des pommes de pin tapissent le chemin. Une fontaine chante, un peu plus loin. Papa pose sa casquette sur le banc. La visière fait un petit coin d'ombre. Amir, tu vois le bois ? Il est tout lisse, tout chaud. On dirait du miel, papa. Oui. J'attends ici, sur le banc. En ce moment, Amir monte les marches. Le bois sent le soleil et la résine. Il glisse. L'air lui chatouille les oreilles. Bravo. Tu as bien glissé. Un enfant arrive trop vite, en bas. Amir sent un choc. Son cœur bat très vite. Stop. Il fait un pas de côté. Il s'éloigne. S'éloigner, c'est marcher vers papa. Amir marche vers le banc. Papa est son parent au parc. Amir rejoint son parent au parc. On m'a bousculé. Papa l'écoute. Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Bravo, Amir. C'est du bon travail. La fontaine chante encore. Oui. On souffle un peu ? Amir souffle. La casquette fait de l'ombre. Plus tard, Amir va près du bac à sable. Il prend une pomme de pin, toute sèche. Je reste ton parent au parc. Je suis sur le banc. Un autre enfant arrive trop vite encore. Amir sent un choc, près du bac. Il se souvient du toboggan. Stop. Il s'éloigne. Il rejoint son parent au parc. Autre coin du parc, même stop. Tu as dit stop. Tu t'es éloigné. Tu es venu vers papa, ton parent au parc. Bravo. Amir pose la pomme de pin sur le banc. Elle sent le bois chaud. La fontaine chante, tout doucement.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Amine est au parc avec papa. Papa s'assoit sur le banc. Amine joue près du toboggan. Un camarade arrive vite. Le camarade bouscule Amine. Amine sent un choc. Son cœur bat vite.
-enfant-f|Stop. Il fait un pas de côté. Il doit s'éloigner. S'éloigner, c'est marcher vers papa.
-narrateur|Amine marche vers le banc. Papa est son parent au parc. Amine rejoint son parent au parc.
-narrateur|On m'a bousculé. Papa l'écoute.
-papa|Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi.
-narrateur|Amine souffle. Plus tard, près du bac à sable, un autre camarade bouscule encore. Amine se souvient.
-narrateur|Stop.
-narrateur|Il s'éloigne. Il rejoint son parent au parc. Même leçon, autre coin du parc. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
+          <t>narrateur|Le toboggan de bois brille comme du miel.
+narrateur|Des pommes de pin tapissent le chemin.
+narrateur|Une fontaine chante, un peu plus loin.
+narrateur|Papa pose sa casquette sur le banc.
+narrateur|La visière fait un petit coin d'ombre.
+papa|Amir, tu vois le bois ?
+papa|Il est tout lisse, tout chaud.
+enfant-m|On dirait du miel, papa.
+papa|Oui.
+papa|J'attends ici, sur le banc.
+narrateur|En ce moment, Amir monte les marches.
+narrateur|Le bois sent le soleil et la résine.
+narrateur|Il glisse.
+narrateur|L'air lui chatouille les oreilles.
+papa|Bravo.
+papa|Tu as bien glissé.
+narrateur|Un enfant arrive trop vite, en bas.
+narrateur|Amir sent un choc.
+narrateur|Son cœur bat très vite.
+enfant-m|Stop.
+narrateur|Il fait un pas de côté.
+narrateur|Il s'éloigne.
+narrateur|S'éloigner, c'est marcher vers papa.
+narrateur|Amir marche vers le banc.
+narrateur|Papa est son parent au parc.
+narrateur|Amir rejoint son parent au parc.
+enfant-m|On m'a bousculé.
+narrateur|Papa l'écoute.
+papa|Tu as dit stop.
+papa|Tu t'es éloigné.
+papa|Tu es venu vers moi.
+papa|Bravo, Amir.
+papa|C'est du bon travail.
+enfant-m|La fontaine chante encore.
+papa|Oui.
+papa|On souffle un peu ?
+narrateur|Amir souffle.
+narrateur|La casquette fait de l'ombre.
+narrateur|Plus tard, Amir va près du bac à sable.
+narrateur|Il prend une pomme de pin, toute sèche.
+papa|Je reste ton parent au parc.
+papa|Je suis sur le banc.
+narrateur|Un autre enfant arrive trop vite encore.
+narrateur|Amir sent un choc, près du bac.
+narrateur|Il se souvient du toboggan.
+enfant-m|Stop.
+narrateur|Il s'éloigne.
+narrateur|Il rejoint son parent au parc.
+papa|Autre coin du parc, même stop.
+papa|Tu as dit stop.
+papa|Tu t'es éloigné.
+papa|Tu es venu vers papa, ton parent au parc.
+papa|Bravo.
+narrateur|Amir pose la pomme de pin sur le banc.
+narrateur|Elle sent le bois chaud.
+narrateur|La fontaine chante, tout doucement.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Amine. Que fait-il ?</t>
+          <t>Un camarade bouscule Amir. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,10 +1567,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Amine. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Un camarade bouscule Amir.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amine a dit stop. Il a su s'éloigner. Il a rejoint son parent au parc. Plus tard, pareil.</t>
+          <t>Amir a dit stop. Il a su s'éloigner. Il a rejoint son parent au parc. Plus tard, pareil, près du bac. Tu es venu vers moi, deux fois. Bravo. Tu as fini de souffler ? Oui, papa. Tu as fait du bon travail. Amir touche la visière de la casquette. Le tissu est un peu rêche, un peu chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1739,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amine a dit stop. Il a su s'éloigner. Il a rejoint son parent au parc. Plus tard, pareil.</t>
+          <t>narrateur|Amir a dit stop.
+narrateur|Il a su s'éloigner.
+narrateur|Il a rejoint son parent au parc.
+narrateur|Plus tard, pareil, près du bac.
+papa|Tu es venu vers moi, deux fois.
+papa|Bravo.
+papa|Tu as fini de souffler ?
+enfant-m|Oui, papa.
+papa|Tu as fait du bon travail.
+narrateur|Amir touche la visière de la casquette.
+narrateur|Le tissu est un peu rêche, un peu chaud.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1711,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amine boit une gorgée d'eau. Papa garde sa main.</t>
+          <t>Papa dévisse la gourde. L'eau fait un petit bruit clair. Tu bois une gorgée ? Oui. Amir boit. L'eau est fraîche. Donne-moi ta main. Papa garde sa main. On écoute la fontaine encore un peu ? Oui, papa. Le toboggan brille comme du miel. La pomme de pin reste sur le banc.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1851,10 +1921,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Amine boit une gorgée d'eau. Papa garde sa main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa dévisse la gourde.
+narrateur|L'eau fait un petit bruit clair.
+papa|Tu bois une gorgée ?
+enfant-m|Oui.
+narrateur|Amir boit.
+narrateur|L'eau est fraîche.
+papa|Donne-moi ta main.
+narrateur|Papa garde sa main.
+papa|On écoute la fontaine encore un peu ?
+enfant-m|Oui, papa.
+narrateur|Le toboggan brille comme du miel.
+narrateur|La pomme de pin reste sur le banc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1879,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis venu vers toi. Bravo, Amir. Tu as fait du bon travail. La fontaine chante encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2019,10 +2099,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|J'ai dit stop.
+enfant-m|Je suis venu vers toi.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+narrateur|La fontaine chante encore.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2041,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2079,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le toboggan de bois brille comme du miel. Des pommes de pin tapissent le chemin. Une fontaine chante, un peu plus loin. Papa pose sa casquette sur le banc. La visière fait un petit coin d'ombre. Amir, tu vois le bois ? Il est tout lisse, tout chaud. On dirait du miel, papa. Oui. J'attends ici, sur le banc. En ce moment, Amir monte les marches. Le bois sent le soleil et la résine. Il glisse. L'air lui chatouille les oreilles. Bravo. Tu as bien glissé. Un enfant arrive trop vite, en bas. Amir sent un choc. Son cœur bat très vite. Stop. Il fait un pas de côté. Il s'éloigne. S'éloigner, c'est marcher vers papa. Amir marche vers le banc. Papa est son parent au parc. Amir rejoint son parent au parc. On m'a bousculé. Papa l'écoute. Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Bravo, Amir. C'est du bon travail. La fontaine chante encore. Oui. On souffle un peu ? Amir souffle. La casquette fait de l'ombre. Plus tard, Amir va près du bac à sable. Il prend une pomme de pin, toute sèche. Je reste ton parent au parc. Je suis sur le banc. Un autre enfant arrive trop vite encore. Amir sent un choc, près du bac. Il se souvient du toboggan. Stop. Il s'éloigne. Il rejoint son parent au parc. Autre coin du parc, même stop. Tu as dit stop. Tu t'es éloigné. Tu es venu vers papa, ton parent au parc. Bravo. Amir pose la pomme de pin sur le banc. Elle sent le bois chaud. La fontaine chante, tout doucement.</t>
+          <t>Le toboggan de bois brille comme du miel. Des pommes de pin tapissent le chemin. Une fontaine chante, un peu plus loin. Papa pose sa casquette sur le banc. La visière fait un petit coin d'ombre. Amir, tu vois le bois ? Il est tout lisse, tout chaud. On dirait du miel, papa. Oui. J'attends ici, sur le banc. En ce moment, Amir monte les marches. Le bois sent le soleil et la résine. Il glisse. L'air lui chatouille les oreilles. Bravo. Tu as bien glissé. Un enfant arrive trop vite, en bas. Amir sent un choc. Son cœur bat très vite. Stop. Il fait un pas de côté. Il s'éloigne. S'éloigner, c'est marcher vers papa. Amir marche vers le banc. Papa est son parent au parc. Amir rejoint son parent au parc. On m'a bousculé. Papa l'écoute. Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Bravo, Amir. La fontaine chante encore. Oui. On souffle un peu ? Amir souffle. La casquette fait de l'ombre. Plus tard, Amir va près du bac à sable. Il prend une pomme de pin, toute sèche. Je reste ton parent au parc. Je suis sur le banc. Un autre enfant arrive trop vite encore. Amir sent un choc, près du bac. Il se souvient du toboggan. Stop. Il s'éloigne. Il rejoint son parent au parc. Autre coin du parc, même stop. Tu as dit stop. Tu t'es éloigné. Tu es venu vers papa, ton parent au parc. Bravo. Amir pose la pomme de pin sur le banc. Elle sent le bois chaud. La fontaine chante, tout doucement.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amine est au parc avec papa. Papa s'assoit sur le banc. Amine joue près du toboggan. Un camarade arrive vite. Le camarade bouscule Amine. Amine sent un choc. Son cœur bat vite. Amine dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Il fait un pas de côté. Il doit s'éloigner. S'éloigner, c'est marcher vers papa. Amine marche vers le banc. Papa est son parent au parc. Amine rejoint son parent au parc. Il dit : on m'a bousculé. Papa l'écoute. Papa dit : tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Amine souffle. Plus tard, près du bac à sable, un autre camarade bouscule encore. Amine se souvient. Il dit : stop. Il s'éloigne. Il rejoint son parent au parc. Même leçon, autre coin du parc. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le toboggan de bois brille comme du miel. Des pommes de pin tapissent le chemin. Une fontaine chante, un peu plus loin. Papa pose sa casquette sur le banc. La visière fait un petit coin d'ombre. Amir, tu vois le bois ? Il est tout lisse, tout chaud. On dirait du miel, papa. Oui. J'attends ici, sur le banc. En ce moment, Amir monte les marches. Le bois sent le soleil et la résine. Il glisse. L'air lui chatouille les oreilles. Bravo. Tu as bien glissé. Un enfant arrive trop vite, en bas. Amir sent un choc. Son cœur bat très vite. Stop. Il fait un pas de côté. Il s'éloigne. S'éloigner, c'est marcher vers papa. Amir marche vers le banc. Papa est son parent au parc. Amir rejoint son parent au parc. On m'a bousculé. Papa l'écoute. Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Bravo, Amir. La fontaine chante encore. Oui. On souffle un peu ? Amir souffle. La casquette fait de l'ombre. Plus tard, Amir va près du bac à sable. Il prend une pomme de pin, toute sèche. Je reste ton parent au parc. Je suis sur le banc. Un autre enfant arrive trop vite encore. Amir sent un choc, près du bac. Il se souvient du toboggan. Stop. Il s'éloigne. Il rejoint son parent au parc. Autre coin du parc, même stop. Tu as dit stop. Tu t'es éloigné. Tu es venu vers papa, ton parent au parc. Bravo. Amir pose la pomme de pin sur le banc. Elle sent le bois chaud. La fontaine chante, tout doucement.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1356,7 +1356,6 @@
 papa|Tu t'es éloigné.
 papa|Tu es venu vers moi.
 papa|Bravo, Amir.
-papa|C'est du bon travail.
 enfant-m|La fontaine chante encore.
 papa|Oui.
 papa|On souffle un peu ?
@@ -1416,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un camarade bouscule Amine. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Amir. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1595,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a dit stop. Il a su s'éloigner. Il a rejoint son parent au parc. Plus tard, pareil, près du bac. Tu es venu vers moi, deux fois. Bravo. Tu as fini de souffler ? Oui, papa. Tu as fait du bon travail. Amir touche la visière de la casquette. Le tissu est un peu rêche, un peu chaud.</t>
+          <t>Amir a dit stop. Il a su s'éloigner. Il a rejoint son parent au parc. Plus tard, pareil, près du bac. Tu es venu vers moi, deux fois. Bravo. Tu as fini de souffler ? Oui, papa. Amir touche la visière de la casquette. Le tissu est un peu rêche, un peu chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amine a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Il a su s'éloigner. Il a rejoint son parent au parc. Plus tard, pareil.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a dit stop. Il a su s'éloigner. Il a rejoint son parent au parc. Plus tard, pareil, près du bac. Tu es venu vers moi, deux fois. Bravo. Tu as fini de souffler ? Oui, papa. Amir touche la visière de la casquette. Le tissu est un peu rêche, un peu chaud.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1747,7 +1746,6 @@
 papa|Bravo.
 papa|Tu as fini de souffler ?
 enfant-m|Oui, papa.
-papa|Tu as fait du bon travail.
 narrateur|Amir touche la visière de la casquette.
 narrateur|Le tissu est un peu rêche, un peu chaud.</t>
         </is>
@@ -1786,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amine boit une gorgée d'eau. Papa garde sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa dévisse la gourde. L'eau fait un petit bruit clair. Tu bois une gorgée ? Oui. Amir boit. L'eau est fraîche. Donne-moi ta main. Papa garde sa main. On écoute la fontaine encore un peu ? Oui, papa. Le toboggan brille comme du miel. La pomme de pin reste sur le banc.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1959,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis venu vers toi. Bravo, Amir. Tu as fait du bon travail. La fontaine chante encore. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis venu vers toi. Bravo, Amir. La fontaine chante encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis venu vers toi. Bravo, Amir. La fontaine chante encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2102,9 +2100,7 @@
           <t>enfant-m|J'ai dit stop.
 enfant-m|Je suis venu vers toi.
 papa|Bravo, Amir.
-papa|Tu as fait du bon travail.
-narrateur|La fontaine chante encore.
-narrateur|L'histoire est finie.</t>
+narrateur|La fontaine chante encore.</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc, toboggan de bois puis bac à sable</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amine, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
